--- a/data/trans_orig/P5708-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5708-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2007</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>449905</t>
+          <t>446099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>511972</t>
+          <t>511622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>566678</t>
+          <t>568402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>638564</t>
+          <t>638793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1038012</t>
+          <t>1035985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1128776</t>
+          <t>1135401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269747</t>
+          <t>269870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>329244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314647</t>
+          <t>313981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376162</t>
+          <t>376420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598175</t>
+          <t>599131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682323</t>
+          <t>688589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162598</t>
+          <t>164676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>211709</t>
+          <t>212746</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>244703</t>
+          <t>244668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303765</t>
+          <t>301564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>425705</t>
+          <t>425149</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>499498</t>
+          <t>500142</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42868</t>
+          <t>42951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71302</t>
+          <t>71706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64600</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101371</t>
+          <t>97770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113753</t>
+          <t>113370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160285</t>
+          <t>159016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>939908</t>
+          <t>939430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1022024</t>
+          <t>1020771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>897818</t>
+          <t>897644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>976355</t>
+          <t>977534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1863740</t>
+          <t>1862222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1976725</t>
+          <t>1978721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424523</t>
+          <t>426908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497381</t>
+          <t>501298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367904</t>
+          <t>367035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437937</t>
+          <t>436030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814171</t>
+          <t>813627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>916070</t>
+          <t>917617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191256</t>
+          <t>190447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242805</t>
+          <t>245607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>176777</t>
+          <t>174042</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230766</t>
+          <t>230619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>382559</t>
+          <t>379184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>459822</t>
+          <t>458509</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20473</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>44276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57962</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56931</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92317</t>
+          <t>91367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>305254</t>
+          <t>307965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>355565</t>
+          <t>354780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>276071</t>
+          <t>275661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>318713</t>
+          <t>317422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>597762</t>
+          <t>596211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>660867</t>
+          <t>661179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129309</t>
+          <t>128930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>170714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92849</t>
+          <t>94495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129026</t>
+          <t>131845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234349</t>
+          <t>234003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>289943</t>
+          <t>290676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71423</t>
+          <t>73154</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>37044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86286</t>
+          <t>86477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126177</t>
+          <t>127950</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2549,97 +2549,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4645</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5223</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1732177</t>
+          <t>1734981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1847536</t>
+          <t>1851462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1783870</t>
+          <t>1781930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1895887</t>
+          <t>1896253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3555654</t>
+          <t>3547712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3723075</t>
+          <t>3710601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>857587</t>
+          <t>858890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>959097</t>
+          <t>962178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>807475</t>
+          <t>805817</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>906453</t>
+          <t>913691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1690214</t>
+          <t>1691308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1831073</t>
+          <t>1837214</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>417947</t>
+          <t>420871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>499413</t>
+          <t>500447</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>485360</t>
+          <t>483733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>570200</t>
+          <t>569322</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>925775</t>
+          <t>928719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1041884</t>
+          <t>1043851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81988</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122402</t>
+          <t>122619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>117016</t>
+          <t>116761</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>163781</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208112</t>
+          <t>211282</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272012</t>
+          <t>272309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27580</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>42690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2012</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>502233</t>
+          <t>500691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>565184</t>
+          <t>565531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>665901</t>
+          <t>665895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>741398</t>
+          <t>741965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1188661</t>
+          <t>1186866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1289370</t>
+          <t>1284967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,79%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233044</t>
+          <t>238058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293113</t>
+          <t>293897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>381648</t>
+          <t>385460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>453499</t>
+          <t>454583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636957</t>
+          <t>640104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>727817</t>
+          <t>728236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100660</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144305</t>
+          <t>144552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134643</t>
+          <t>131740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182643</t>
+          <t>181419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>250280</t>
+          <t>249866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313862</t>
+          <t>313306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46177</t>
+          <t>45515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>50290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52552</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87183</t>
+          <t>87216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25982</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>50163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1153097</t>
+          <t>1153011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1242605</t>
+          <t>1241444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>954605</t>
+          <t>956239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1039819</t>
+          <t>1044513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2136589</t>
+          <t>2138984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2253468</t>
+          <t>2264503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471741</t>
+          <t>470609</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>551426</t>
+          <t>548485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497540</t>
+          <t>499629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576492</t>
+          <t>578495</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988469</t>
+          <t>986080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1098525</t>
+          <t>1101416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169628</t>
+          <t>170552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>224740</t>
+          <t>228033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143727</t>
+          <t>143671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194621</t>
+          <t>192851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327304</t>
+          <t>323169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>401683</t>
+          <t>400571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57371</t>
+          <t>56636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53055</t>
+          <t>53287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62953</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100705</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>289818</t>
+          <t>288635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>334951</t>
+          <t>336359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>279831</t>
+          <t>282061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>325917</t>
+          <t>323879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>587244</t>
+          <t>585058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>649843</t>
+          <t>650127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94797</t>
+          <t>91716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133254</t>
+          <t>130856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96830</t>
+          <t>98499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138579</t>
+          <t>135722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>199956</t>
+          <t>202258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257425</t>
+          <t>257304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>58774</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49921</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>60827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98378</t>
+          <t>97181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,77 +5528,77 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4940</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5974</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6859</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1988511</t>
+          <t>1991326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2109468</t>
+          <t>2108494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1947283</t>
+          <t>1944954</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2070368</t>
+          <t>2072431</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3960136</t>
+          <t>3972233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4134660</t>
+          <t>4140974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>829686</t>
+          <t>832219</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>939246</t>
+          <t>939960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1012658</t>
+          <t>1012399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1128448</t>
+          <t>1134675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1881357</t>
+          <t>1880341</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2037331</t>
+          <t>2033536</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>324340</t>
+          <t>323455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>403286</t>
+          <t>399137</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>327226</t>
+          <t>325738</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>401538</t>
+          <t>397139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>667799</t>
+          <t>672376</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>773947</t>
+          <t>774733</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>103442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>60057</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97144</t>
+          <t>98056</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134642</t>
+          <t>134405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185802</t>
+          <t>186682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>43125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80115</t>
+          <t>75143</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2016</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343953</t>
+          <t>343454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396608</t>
+          <t>395826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>384776</t>
+          <t>381818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>451185</t>
+          <t>444800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>745981</t>
+          <t>743986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>830484</t>
+          <t>829109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191596</t>
+          <t>191111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239312</t>
+          <t>240497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304594</t>
+          <t>304959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>365322</t>
+          <t>365628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509476</t>
+          <t>510949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>590025</t>
+          <t>593549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114295</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155381</t>
+          <t>159346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154976</t>
+          <t>155288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203895</t>
+          <t>202846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282756</t>
+          <t>280185</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>348859</t>
+          <t>344648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68443</t>
+          <t>69445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64474</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100179</t>
+          <t>103200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>972371</t>
+          <t>964813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1068579</t>
+          <t>1057932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>956100</t>
+          <t>950650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1042315</t>
+          <t>1041883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1957738</t>
+          <t>1951683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2086220</t>
+          <t>2079062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635839</t>
+          <t>638991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>725133</t>
+          <t>728807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616295</t>
+          <t>610147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699485</t>
+          <t>695677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1275168</t>
+          <t>1279597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1401616</t>
+          <t>1397998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282575</t>
+          <t>282637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>347956</t>
+          <t>351609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>261947</t>
+          <t>259685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324370</t>
+          <t>326757</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>564490</t>
+          <t>564542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>654275</t>
+          <t>655870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76017</t>
+          <t>76341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,47 +7835,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>24581</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>15045</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>36433</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>24581</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>16164</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>36753</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284877</t>
+          <t>284385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>331600</t>
+          <t>332202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>311086</t>
+          <t>311942</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358503</t>
+          <t>358539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>608668</t>
+          <t>611517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>677551</t>
+          <t>674190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154590</t>
+          <t>154275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200679</t>
+          <t>201307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131581</t>
+          <t>131617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175381</t>
+          <t>172740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296565</t>
+          <t>298588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359853</t>
+          <t>358550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77513</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37034</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65899</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89451</t>
+          <t>88280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134518</t>
+          <t>132946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1639310</t>
+          <t>1632757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1757001</t>
+          <t>1753580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1686886</t>
+          <t>1681640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1811709</t>
+          <t>1812727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3360428</t>
+          <t>3351926</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3525033</t>
+          <t>3522227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1018692</t>
+          <t>1018030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1127762</t>
+          <t>1133701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1089471</t>
+          <t>1088828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1203188</t>
+          <t>1199286</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2133624</t>
+          <t>2141963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2294760</t>
+          <t>2297971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>469315</t>
+          <t>468311</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>556117</t>
+          <t>551836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>483589</t>
+          <t>477369</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>565658</t>
+          <t>565199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>975447</t>
+          <t>977687</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1094949</t>
+          <t>1103587</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51230</t>
+          <t>50587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83908</t>
+          <t>85032</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>105933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124675</t>
+          <t>126362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175544</t>
+          <t>175567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33613</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57325</t>
+          <t>55924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2023</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>247754</t>
+          <t>249414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290568</t>
+          <t>292866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>362526</t>
+          <t>360623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>404402</t>
+          <t>403167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>622693</t>
+          <t>624136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>684266</t>
+          <t>681476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108483</t>
+          <t>106617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>145019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172104</t>
+          <t>172338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207326</t>
+          <t>209141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>291380</t>
+          <t>291796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>342197</t>
+          <t>339134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90560</t>
+          <t>88465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92706</t>
+          <t>91866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119506</t>
+          <t>120529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159152</t>
+          <t>160523</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>198675</t>
+          <t>201029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57555</t>
+          <t>57758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64649</t>
+          <t>65026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90044</t>
+          <t>91784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>40420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1419239</t>
+          <t>1412206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1769767</t>
+          <t>1756935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>896015</t>
+          <t>920001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1431906</t>
+          <t>1437911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2467153</t>
+          <t>2428832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3065546</t>
+          <t>3054874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>368982</t>
+          <t>377175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625830</t>
+          <t>629138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381153</t>
+          <t>390571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>591644</t>
+          <t>597092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848266</t>
+          <t>845015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1172805</t>
+          <t>1182805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109147</t>
+          <t>110387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>193713</t>
+          <t>196574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,17 +10548,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359909</t>
+          <t>359910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162585</t>
+          <t>158345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>927532</t>
+          <t>881831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>308815</t>
+          <t>307601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1125148</t>
+          <t>1111416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64417</t>
+          <t>64802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,47 +10681,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>87320</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>69165</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>108511</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>87320</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>67201</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>106821</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>31766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54724</t>
+          <t>54982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2225125</t>
+          <t>2225126</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2225125</t>
+          <t>2225126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2225125</t>
+          <t>2225126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>404566</t>
+          <t>407355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>459218</t>
+          <t>460430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>446649</t>
+          <t>449584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>487076</t>
+          <t>487515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>867430</t>
+          <t>867966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>935379</t>
+          <t>937137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131697</t>
+          <t>130915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176070</t>
+          <t>176958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138853</t>
+          <t>138436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175972</t>
+          <t>174835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277964</t>
+          <t>276371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337596</t>
+          <t>334708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>44371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35494</t>
+          <t>35238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>41478</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>72216</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25448</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31172</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>328</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>54456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2119724</t>
+          <t>2110480</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2521016</t>
+          <t>2489752</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1762239</t>
+          <t>1731341</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2285217</t>
+          <t>2278610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3995039</t>
+          <t>3931476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4631265</t>
+          <t>4604700</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>633062</t>
+          <t>632366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>906333</t>
+          <t>910868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>705965</t>
+          <t>711946</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>936396</t>
+          <t>935858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1449439</t>
+          <t>1458591</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1812001</t>
+          <t>1804866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>210185</t>
+          <t>209445</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303103</t>
+          <t>305969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>290510</t>
+          <t>293557</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1066391</t>
+          <t>1063203</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>536357</t>
+          <t>542135</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1431457</t>
+          <t>1526636</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59709</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99514</t>
+          <t>99469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84834</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123213</t>
+          <t>120715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153207</t>
+          <t>155959</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210132</t>
+          <t>211578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>28338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73952</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32588</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57836</t>
+          <t>57734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>67197</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119619</t>
+          <t>116782</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5708-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5708-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>446099</t>
+          <t>448867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>511622</t>
+          <t>511751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>568402</t>
+          <t>566772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>638793</t>
+          <t>640141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1035985</t>
+          <t>1036595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1135401</t>
+          <t>1129410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269870</t>
+          <t>268422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329244</t>
+          <t>326024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>313981</t>
+          <t>313776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376420</t>
+          <t>375702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>599131</t>
+          <t>600083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>688589</t>
+          <t>682260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164676</t>
+          <t>166101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>212746</t>
+          <t>213946</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>244668</t>
+          <t>245750</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>301564</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>425149</t>
+          <t>421720</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>500142</t>
+          <t>501538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42951</t>
+          <t>42700</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71706</t>
+          <t>72706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63619</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97770</t>
+          <t>98350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113370</t>
+          <t>115759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159016</t>
+          <t>160353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35210</t>
+          <t>34157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>939430</t>
+          <t>939474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1020771</t>
+          <t>1022562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>897644</t>
+          <t>897059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>977534</t>
+          <t>979834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1862222</t>
+          <t>1854288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1978721</t>
+          <t>1976719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426908</t>
+          <t>425461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501298</t>
+          <t>497420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367035</t>
+          <t>368577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>436030</t>
+          <t>438507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813627</t>
+          <t>818004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>917617</t>
+          <t>924907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190447</t>
+          <t>190823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245607</t>
+          <t>242646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174042</t>
+          <t>176266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230619</t>
+          <t>231731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>379184</t>
+          <t>381061</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>458509</t>
+          <t>455629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44276</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57644</t>
+          <t>58514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57392</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91367</t>
+          <t>91908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,47 +1882,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9057</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8479</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>307965</t>
+          <t>304511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>354780</t>
+          <t>353910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275661</t>
+          <t>275481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317422</t>
+          <t>318129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>596211</t>
+          <t>597170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>661179</t>
+          <t>660398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128930</t>
+          <t>129345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170714</t>
+          <t>172758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94495</t>
+          <t>93786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131845</t>
+          <t>132206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234003</t>
+          <t>233640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>290676</t>
+          <t>289745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>41379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73154</t>
+          <t>71877</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63892</t>
+          <t>65778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86477</t>
+          <t>87725</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127950</t>
+          <t>127204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26878</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>20151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1734981</t>
+          <t>1735010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1851462</t>
+          <t>1851492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1781930</t>
+          <t>1781648</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1896253</t>
+          <t>1896141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3547712</t>
+          <t>3551844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3710601</t>
+          <t>3718054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>858890</t>
+          <t>860556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>962178</t>
+          <t>968126</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>805817</t>
+          <t>808400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>913691</t>
+          <t>907610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1691308</t>
+          <t>1698148</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1837214</t>
+          <t>1840295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>420871</t>
+          <t>424127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>500447</t>
+          <t>502512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>483733</t>
+          <t>478877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>569322</t>
+          <t>568429</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>928719</t>
+          <t>926567</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1043851</t>
+          <t>1044738</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82329</t>
+          <t>82429</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122619</t>
+          <t>122350</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116761</t>
+          <t>116894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>163897</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211282</t>
+          <t>211162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272309</t>
+          <t>274099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42690</t>
+          <t>42103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500691</t>
+          <t>502265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>565531</t>
+          <t>566924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>665895</t>
+          <t>667864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>741965</t>
+          <t>742333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1186866</t>
+          <t>1191714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1284967</t>
+          <t>1287939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238058</t>
+          <t>233560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293897</t>
+          <t>292803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385460</t>
+          <t>383586</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>454583</t>
+          <t>451261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640104</t>
+          <t>632900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728236</t>
+          <t>727440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103230</t>
+          <t>101772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144552</t>
+          <t>145429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131740</t>
+          <t>135779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>181419</t>
+          <t>185805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249866</t>
+          <t>246458</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313306</t>
+          <t>313504</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>51521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>55355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>89633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>25342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50163</t>
+          <t>51172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1153011</t>
+          <t>1151028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1241444</t>
+          <t>1241792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>956239</t>
+          <t>952812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1044513</t>
+          <t>1041047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2138984</t>
+          <t>2135738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2264503</t>
+          <t>2256658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470609</t>
+          <t>470008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>548485</t>
+          <t>548387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499629</t>
+          <t>502062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>578495</t>
+          <t>580642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>986080</t>
+          <t>991439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1101416</t>
+          <t>1104376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170552</t>
+          <t>168539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228033</t>
+          <t>226133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143671</t>
+          <t>141918</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192851</t>
+          <t>196584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>323169</t>
+          <t>325134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>400571</t>
+          <t>400324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>57590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53287</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62595</t>
+          <t>64745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>102192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33548</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288635</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>336359</t>
+          <t>336569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>282061</t>
+          <t>280689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>323879</t>
+          <t>323800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>585058</t>
+          <t>587768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>650127</t>
+          <t>650244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91716</t>
+          <t>94084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130856</t>
+          <t>132787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135722</t>
+          <t>136344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202258</t>
+          <t>200624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257304</t>
+          <t>256714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28676</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58774</t>
+          <t>60691</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49814</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60827</t>
+          <t>61675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97181</t>
+          <t>101175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1991326</t>
+          <t>1990473</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2108494</t>
+          <t>2107786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1944954</t>
+          <t>1945084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2072431</t>
+          <t>2066833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3972233</t>
+          <t>3967203</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4140974</t>
+          <t>4128388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>832219</t>
+          <t>839744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>939960</t>
+          <t>940196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1012399</t>
+          <t>1014666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1134675</t>
+          <t>1126056</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1880341</t>
+          <t>1884437</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2033536</t>
+          <t>2026896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>323455</t>
+          <t>324939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>399137</t>
+          <t>399779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>325738</t>
+          <t>327555</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>397139</t>
+          <t>403236</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>672376</t>
+          <t>668166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>774733</t>
+          <t>773919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64964</t>
+          <t>64632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>102224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60057</t>
+          <t>61250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98056</t>
+          <t>97907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134405</t>
+          <t>134020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186682</t>
+          <t>187897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>37038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49431</t>
+          <t>49477</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,47 +6240,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>58706</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>44846</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>76755</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>43125</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>75143</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343454</t>
+          <t>342126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>395826</t>
+          <t>397597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381818</t>
+          <t>385387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444800</t>
+          <t>448296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>743986</t>
+          <t>741787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>829109</t>
+          <t>827682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191111</t>
+          <t>193233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240497</t>
+          <t>238446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304959</t>
+          <t>302658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>365628</t>
+          <t>368036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510949</t>
+          <t>511930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593549</t>
+          <t>590762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116201</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159346</t>
+          <t>156767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>154048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>202846</t>
+          <t>204306</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280185</t>
+          <t>282675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344648</t>
+          <t>348383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42882</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37551</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>68791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>64194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103200</t>
+          <t>102457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,47 +7153,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>14039</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>26164</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>14039</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>7307</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>23916</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>964813</t>
+          <t>971996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1057932</t>
+          <t>1063112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>950650</t>
+          <t>956484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1041883</t>
+          <t>1044963</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1951683</t>
+          <t>1956452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2079062</t>
+          <t>2083583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638991</t>
+          <t>643910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728807</t>
+          <t>725508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610147</t>
+          <t>615057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>695677</t>
+          <t>702803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1279597</t>
+          <t>1276513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1397998</t>
+          <t>1399112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282637</t>
+          <t>282570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>351609</t>
+          <t>350858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259685</t>
+          <t>258596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>326757</t>
+          <t>322906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>564542</t>
+          <t>564800</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>655870</t>
+          <t>662654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>23706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>49514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>36525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76341</t>
+          <t>76133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>36877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284385</t>
+          <t>283568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332202</t>
+          <t>331027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>311942</t>
+          <t>312172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358539</t>
+          <t>357292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>611517</t>
+          <t>610799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>674190</t>
+          <t>678148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154275</t>
+          <t>153710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201307</t>
+          <t>199058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131617</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172740</t>
+          <t>174561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298588</t>
+          <t>296394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358550</t>
+          <t>359150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75813</t>
+          <t>76536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37261</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88280</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132946</t>
+          <t>133150</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1632757</t>
+          <t>1630616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1753580</t>
+          <t>1752544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1681640</t>
+          <t>1689840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1812727</t>
+          <t>1813560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3351926</t>
+          <t>3354338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3522227</t>
+          <t>3533122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1018030</t>
+          <t>1016169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1133701</t>
+          <t>1132716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1088828</t>
+          <t>1087438</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1199286</t>
+          <t>1196778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2141963</t>
+          <t>2133235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2297971</t>
+          <t>2296840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>468311</t>
+          <t>472072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>551836</t>
+          <t>557899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>477369</t>
+          <t>480961</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>565199</t>
+          <t>564498</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>974117</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1103587</t>
+          <t>1096300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>51844</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>84678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,82 +9051,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>83436</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>65709</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>102406</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>149121</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>123235</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>173877</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>83436</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>66708</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>105933</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>149121</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>126362</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>175567</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55924</t>
+          <t>57013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>271577</t>
+          <t>301392</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>249414</t>
+          <t>278487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>292866</t>
+          <t>325148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>382130</t>
+          <t>409254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>360623</t>
+          <t>385998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>403167</t>
+          <t>431579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>653707</t>
+          <t>710646</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>624136</t>
+          <t>678078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>681476</t>
+          <t>742747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125320</t>
+          <t>138090</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>118864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145019</t>
+          <t>158065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>190191</t>
+          <t>209553</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172338</t>
+          <t>189550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209141</t>
+          <t>227838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>315510</t>
+          <t>347642</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>291796</t>
+          <t>319677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339134</t>
+          <t>374794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74363</t>
+          <t>85209</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60489</t>
+          <t>69869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88465</t>
+          <t>100366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104989</t>
+          <t>116067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91866</t>
+          <t>102123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120529</t>
+          <t>131823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>179352</t>
+          <t>201276</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>160523</t>
+          <t>179871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201029</t>
+          <t>224249</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>53788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47639</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>64922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>76439</t>
+          <t>90173</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65026</t>
+          <t>74162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91784</t>
+          <t>109388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22711</t>
+          <t>27290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40420</t>
+          <t>45746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510430</t>
+          <t>573732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510430</t>
+          <t>573732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510430</t>
+          <t>573732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>745333</t>
+          <t>811331</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>745333</t>
+          <t>811331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>745333</t>
+          <t>811331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1255763</t>
+          <t>1385063</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1255763</t>
+          <t>1385063</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1255763</t>
+          <t>1385063</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1526278</t>
+          <t>1372238</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1412206</t>
+          <t>1317572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1756935</t>
+          <t>1422065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1280609</t>
+          <t>1316528</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>920001</t>
+          <t>1276994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1437911</t>
+          <t>1361309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2806887</t>
+          <t>2688765</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2428832</t>
+          <t>2623734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3054874</t>
+          <t>2753094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>62,8%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>543707</t>
+          <t>605235</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377175</t>
+          <t>559298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629138</t>
+          <t>654415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>515882</t>
+          <t>584075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390571</t>
+          <t>545369</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>597092</t>
+          <t>623171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1059589</t>
+          <t>1189310</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>845015</t>
+          <t>1132572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1182805</t>
+          <t>1249373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158031</t>
+          <t>175104</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110387</t>
+          <t>147907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196574</t>
+          <t>206804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359910</t>
+          <t>175570</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158345</t>
+          <t>152384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>881831</t>
+          <t>200012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>517940</t>
+          <t>350674</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307601</t>
+          <t>314417</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1111416</t>
+          <t>388501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37206</t>
+          <t>47818</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>35746</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>63414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50115</t>
+          <t>57187</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>45240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64802</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87320</t>
+          <t>105005</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69165</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108511</t>
+          <t>125202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>50170</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27753</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54982</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2286666</t>
+          <t>2225363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2286666</t>
+          <t>2225363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2286666</t>
+          <t>2225363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2225126</t>
+          <t>2158561</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2225126</t>
+          <t>2158561</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2225126</t>
+          <t>2158561</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4511792</t>
+          <t>4383924</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4511792</t>
+          <t>4383924</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4511792</t>
+          <t>4383924</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>435097</t>
+          <t>483365</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>407355</t>
+          <t>456918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>460430</t>
+          <t>509307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>467701</t>
+          <t>516601</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>449584</t>
+          <t>496033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>487515</t>
+          <t>538634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>902798</t>
+          <t>999966</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>867966</t>
+          <t>962432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>937137</t>
+          <t>1032944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>152479</t>
+          <t>169174</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130915</t>
+          <t>147297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176958</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>155958</t>
+          <t>177085</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138436</t>
+          <t>156348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174835</t>
+          <t>196236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>308436</t>
+          <t>346259</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276371</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334708</t>
+          <t>379193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>50518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>55508</t>
+          <t>62400</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41478</t>
+          <t>49580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>80642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26371</t>
+          <t>27049</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>34479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54456</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>642120</t>
+          <t>707088</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>642120</t>
+          <t>707088</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>642120</t>
+          <t>707088</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658547</t>
+          <t>732329</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658547</t>
+          <t>732329</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658547</t>
+          <t>732329</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1300666</t>
+          <t>1439417</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1300666</t>
+          <t>1439417</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1300666</t>
+          <t>1439417</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2232952</t>
+          <t>2156994</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2110480</t>
+          <t>2098038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2489752</t>
+          <t>2220597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2130440</t>
+          <t>2242382</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1731341</t>
+          <t>2189211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2278610</t>
+          <t>2293935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4363392</t>
+          <t>4399376</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3931476</t>
+          <t>4321077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4604700</t>
+          <t>4485156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>821505</t>
+          <t>912498</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632366</t>
+          <t>856660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>910868</t>
+          <t>967821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>862031</t>
+          <t>970713</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711946</t>
+          <t>925019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>935858</t>
+          <t>1016579</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1683536</t>
+          <t>1883211</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1458591</t>
+          <t>1806753</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1804866</t>
+          <t>1954948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>263330</t>
+          <t>296267</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209445</t>
+          <t>262099</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>305969</t>
+          <t>336598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>489471</t>
+          <t>318083</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293557</t>
+          <t>289652</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1063203</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>752801</t>
+          <t>614350</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>542135</t>
+          <t>569337</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1526636</t>
+          <t>660970</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>79022</t>
+          <t>98738</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58641</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99469</t>
+          <t>121117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>103764</t>
+          <t>118291</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81723</t>
+          <t>103064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>120715</t>
+          <t>136473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>182786</t>
+          <t>217029</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155959</t>
+          <t>188781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211578</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>41685</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28338</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77045</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43299</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57734</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>94437</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67197</t>
+          <t>77867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116782</t>
+          <t>114168</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3439216</t>
+          <t>3506183</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3439216</t>
+          <t>3506183</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3439216</t>
+          <t>3506183</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3629005</t>
+          <t>3702221</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3629005</t>
+          <t>3702221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3629005</t>
+          <t>3702221</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7068221</t>
+          <t>7208403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7068221</t>
+          <t>7208403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7068221</t>
+          <t>7208403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
